--- a/data/trans_camb/P16A09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,56</t>
+          <t>-3,09; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,48</t>
+          <t>-3,6; 1,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -1,13</t>
+          <t>-5,09; -0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,72</t>
+          <t>-4,4; 2,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,89</t>
+          <t>-4,05; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,68</t>
+          <t>-4,63; 1,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,42</t>
+          <t>-3,07; 1,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,46</t>
+          <t>-2,99; 1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,36</t>
+          <t>-4,22; -0,48</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-86,15; 104,9</t>
+          <t>-80,14; 203,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,29; 125,53</t>
+          <t>-81,21; 109,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,24</t>
+          <t>-100,0; -23,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 120,34</t>
+          <t>-68,82; 111,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 111,52</t>
+          <t>-63,18; 112,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,99; 67,96</t>
+          <t>-64,2; 61,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 56,31</t>
+          <t>-64,9; 56,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 60,64</t>
+          <t>-61,17; 50,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,32; -8,67</t>
+          <t>-78,1; -15,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,36</t>
+          <t>0,19; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,74</t>
+          <t>-0,88; 1,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,94</t>
+          <t>-1,6; 0,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,37</t>
+          <t>-3,44; 2,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,25</t>
+          <t>-5,36; -0,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,74</t>
+          <t>-6,32; -1,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,41</t>
+          <t>-1,08; 2,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,34</t>
+          <t>-2,66; 0,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,87</t>
+          <t>-3,46; -0,88</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 1105,08</t>
+          <t>-6,29; 1099,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 477,52</t>
+          <t>-62,99; 534,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-93,59; 459,74</t>
+          <t>-100,0; 286,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 56,63</t>
+          <t>-47,57; 55,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,08; -5,3</t>
+          <t>-72,63; -5,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,07; -36,83</t>
+          <t>-83,38; -37,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 91,71</t>
+          <t>-26,18; 95,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 13,84</t>
+          <t>-62,69; 18,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,16; -30,17</t>
+          <t>-80,33; -31,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,08</t>
+          <t>-1,21; 2,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,87</t>
+          <t>-0,87; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,36</t>
+          <t>-1,19; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,74</t>
+          <t>0,62; 7,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,38</t>
+          <t>-1,37; 3,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,58</t>
+          <t>-0,3; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,85</t>
+          <t>0,25; 3,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,72</t>
+          <t>-0,59; 2,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,85</t>
+          <t>0,01; 2,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 422,98</t>
+          <t>-76,26; 525,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 527,49</t>
+          <t>-52,36; 688,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 632,49</t>
+          <t>-61,91; 519,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,18; 560,32</t>
+          <t>-0,17; 557,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 260,86</t>
+          <t>-43,16; 343,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 339,92</t>
+          <t>-13,06; 361,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 319,41</t>
+          <t>4,06; 356,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 247,25</t>
+          <t>-29,96; 269,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 269,7</t>
+          <t>-4,84; 307,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,94</t>
+          <t>-0,93; 3,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,71</t>
+          <t>-2,5; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 4,34</t>
+          <t>-0,97; 4,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,29</t>
+          <t>-0,18; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,74</t>
+          <t>-2,83; 3,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,4</t>
+          <t>-3,32; 2,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,16</t>
+          <t>0,26; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,7</t>
+          <t>-1,96; 1,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,52</t>
+          <t>-1,42; 2,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,16; 348,48</t>
+          <t>-39,57; 407,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-81,0; 196,29</t>
+          <t>-83,42; 179,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 403,02</t>
+          <t>-45,79; 445,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 226,12</t>
+          <t>-6,36; 244,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 95,36</t>
+          <t>-52,72; 126,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 87,15</t>
+          <t>-56,18; 96,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1; 183,39</t>
+          <t>2,53; 179,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 78,51</t>
+          <t>-49,47; 70,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,69; 113,0</t>
+          <t>-36,18; 103,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,51</t>
+          <t>-4,76; 3,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -2,03</t>
+          <t>-8,6; -2,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,68; -1,37</t>
+          <t>-7,58; -1,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 5,36</t>
+          <t>-6,94; 5,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 1,31</t>
+          <t>-9,45; 1,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -2,1</t>
+          <t>-11,97; -2,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,4</t>
+          <t>-4,12; 3,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,59; -1,3</t>
+          <t>-7,66; -1,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -2,39</t>
+          <t>-8,12; -2,45</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-78,0; 162,88</t>
+          <t>-75,39; 179,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,4</t>
+          <t>-100,0; -9,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 77,26</t>
+          <t>-50,68; 76,84</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,87; 28,3</t>
+          <t>-74,43; 32,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,03; -31,07</t>
+          <t>-81,07; -33,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 70,9</t>
+          <t>-44,66; 61,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-80,03; -16,43</t>
+          <t>-81,98; -22,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,31; -46,54</t>
+          <t>-82,87; -46,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,77</t>
+          <t>-2,12; 2,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,38</t>
+          <t>-2,43; 2,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,44</t>
+          <t>-1,78; 2,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,8</t>
+          <t>-1,35; 6,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,61</t>
+          <t>-2,02; 4,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,5</t>
+          <t>-1,44; 4,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,31</t>
+          <t>-1,35; 3,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,71</t>
+          <t>-1,61; 2,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,76</t>
+          <t>-0,77; 2,79</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-71,73; 261,52</t>
+          <t>-72,99; 255,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 280,5</t>
+          <t>-79,81; 282,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 287,73</t>
+          <t>-57,33; 291,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,84; 261,06</t>
+          <t>-29,45; 296,33</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 210,3</t>
+          <t>-41,3; 233,62</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 225,34</t>
+          <t>-27,98; 227,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 166,17</t>
+          <t>-36,59; 153,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 140,81</t>
+          <t>-42,25; 143,3</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 145,73</t>
+          <t>-21,43; 143,57</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -1,16</t>
+          <t>-4,61; -0,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,66</t>
+          <t>-4,5; -0,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,06</t>
+          <t>-3,74; -0,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,38</t>
+          <t>-1,08; 3,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,7</t>
+          <t>-2,29; 1,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,63</t>
+          <t>-3,04; 1,8</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,61</t>
+          <t>-2,43; 0,63</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,07</t>
+          <t>-2,99; -0,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,38</t>
+          <t>-2,82; 0,32</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-87,76; -33,0</t>
+          <t>-86,58; -26,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,5; -19,57</t>
+          <t>-83,68; -24,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-72,17; 1,6</t>
+          <t>-72,43; -0,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 118,08</t>
+          <t>-23,38; 125,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 65,09</t>
+          <t>-49,62; 64,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 50,97</t>
+          <t>-60,16; 58,76</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 19,88</t>
+          <t>-51,29; 19,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,57; -1,76</t>
+          <t>-60,92; -1,03</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,79; 10,45</t>
+          <t>-57,41; 10,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -1,24</t>
+          <t>-4,62; -1,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,22; -2,39</t>
+          <t>-5,41; -2,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,48</t>
+          <t>-4,61; -0,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,74</t>
+          <t>-3,2; 2,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,61</t>
+          <t>-5,24; -0,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,9</t>
+          <t>2,1; 7,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,29</t>
+          <t>-3,2; -0,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -1,85</t>
+          <t>-4,89; -1,92</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,67</t>
+          <t>-2,24; 2,56</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-84,53; -33,44</t>
+          <t>-84,89; -39,64</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-97,66; -64,04</t>
+          <t>-97,51; -59,09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-83,65; -17,71</t>
+          <t>-82,25; -21,29</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 32,16</t>
+          <t>-39,18; 39,11</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-65,2; -10,31</t>
+          <t>-65,07; -11,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,97; 150,54</t>
+          <t>23,29; 144,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-53,53; -5,42</t>
+          <t>-50,27; -2,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-75,44; -39,28</t>
+          <t>-75,29; -40,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 54,25</t>
+          <t>-36,28; 53,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,71; -0,03</t>
+          <t>-1,57; -0,11</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; -0,88</t>
+          <t>-2,28; -0,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,39</t>
+          <t>-1,91; -0,43</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,89</t>
+          <t>-0,29; 1,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,32</t>
+          <t>-2,3; -0,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,02</t>
+          <t>-1,17; 1,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,67</t>
+          <t>-0,75; 0,64</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,79</t>
+          <t>-2,07; -0,76</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,1</t>
+          <t>-1,22; 0,17</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-49,99; -0,8</t>
+          <t>-47,73; -3,3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-68,52; -34,48</t>
+          <t>-69,12; -35,13</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,79; -15,98</t>
+          <t>-57,57; -16,46</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 42,16</t>
+          <t>-5,0; 44,72</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -6,12</t>
+          <t>-41,15; -6,34</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 22,36</t>
+          <t>-20,76; 26,18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 18,43</t>
+          <t>-17,57; 17,09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-46,32; -21,57</t>
+          <t>-47,11; -20,6</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 2,89</t>
+          <t>-28,53; 4,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-2,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,1</t>
+          <t>-3,59; 1,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,33</t>
+          <t>-3,62; 1,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,99</t>
+          <t>-5,49; -1,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,72</t>
+          <t>-4,48; 2,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,81</t>
+          <t>-4,26; 2,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 1,43</t>
+          <t>-4,31; 1,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,32</t>
+          <t>-3,15; 1,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,21</t>
+          <t>-3,15; 1,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,48</t>
+          <t>-4,23; -0,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-91,83%</t>
+          <t>-92,95%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,5%</t>
+          <t>-31,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-53,92%</t>
+          <t>-56,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 203,97</t>
+          <t>-81,95; 116,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 109,29</t>
+          <t>-81,98; 102,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -23,94</t>
+          <t>-100,0; -40,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 111,98</t>
+          <t>-67,7; 132,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 112,95</t>
+          <t>-65,41; 107,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 61,43</t>
+          <t>-64,3; 67,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 56,42</t>
+          <t>-65,52; 44,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 50,04</t>
+          <t>-63,89; 51,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,1; -15,55</t>
+          <t>-77,27; -18,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-2,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,34</t>
+          <t>0,03; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,7</t>
+          <t>-0,87; 1,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,85</t>
+          <t>-1,44; 0,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,25</t>
+          <t>-3,52; 2,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,34</t>
+          <t>-5,02; -0,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; -1,67</t>
+          <t>-6,26; -1,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,41</t>
+          <t>-1,04; 2,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,37</t>
+          <t>-2,84; 0,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,88</t>
+          <t>-3,49; -0,98</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,19%</t>
+          <t>-33,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-67,55%</t>
+          <t>-68,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-62,67%</t>
+          <t>-63,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1099,49</t>
+          <t>-16,3; 938,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 534,24</t>
+          <t>-65,98; 491,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 286,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 55,07</t>
+          <t>-49,2; 50,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,63; -5,56</t>
+          <t>-73,43; 0,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,38; -37,06</t>
+          <t>-84,4; -38,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 95,07</t>
+          <t>-24,39; 95,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,69; 18,91</t>
+          <t>-66,06; 6,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-80,33; -31,05</t>
+          <t>-81,16; -37,39</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,24</t>
+          <t>-1,19; 2,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,95</t>
+          <t>-0,78; 3,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,15</t>
+          <t>-1,09; 2,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,11</t>
+          <t>0,95; 6,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,97</t>
+          <t>-1,25; 4,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,4</t>
+          <t>-0,16; 4,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,9</t>
+          <t>0,24; 3,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,75</t>
+          <t>-0,56; 2,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,96</t>
+          <t>-0,27; 2,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 525,26</t>
+          <t>-81,05; 632,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 688,18</t>
+          <t>-48,44; 750,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 519,0</t>
+          <t>-59,89; 639,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 557,73</t>
+          <t>17,25; 547,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 343,51</t>
+          <t>-42,51; 356,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 361,99</t>
+          <t>-12,73; 367,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 356,76</t>
+          <t>4,34; 338,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 269,05</t>
+          <t>-30,26; 219,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 307,43</t>
+          <t>-16,49; 238,68</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,74</t>
+          <t>-1,13; 3,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,7</t>
+          <t>-2,25; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,25</t>
+          <t>-1,44; 3,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 6,9</t>
+          <t>0,1; 6,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 3,28</t>
+          <t>-2,71; 2,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,7</t>
+          <t>-1,81; 3,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,24</t>
+          <t>0,46; 4,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,57</t>
+          <t>-1,81; 1,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,44</t>
+          <t>-0,95; 2,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 407,46</t>
+          <t>-45,98; 313,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 179,49</t>
+          <t>-76,51; 257,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 445,94</t>
+          <t>-51,01; 313,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 244,39</t>
+          <t>-1,42; 220,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,72; 126,27</t>
+          <t>-49,49; 109,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 96,11</t>
+          <t>-37,12; 141,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 179,46</t>
+          <t>10,13; 193,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 70,89</t>
+          <t>-47,56; 79,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 103,15</t>
+          <t>-26,74; 112,49</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,59</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-5,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,39</t>
+          <t>-4,89; 3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -2,01</t>
+          <t>-8,34; -2,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,19</t>
+          <t>-7,74; -1,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 5,23</t>
+          <t>-6,49; 5,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,53</t>
+          <t>-9,71; 1,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,97; -2,38</t>
+          <t>-11,77; -2,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,12</t>
+          <t>-4,29; 3,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -1,31</t>
+          <t>-7,92; -1,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,12; -2,45</t>
+          <t>-8,13; -2,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-85,01%</t>
+          <t>-86,6%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-63,76%</t>
+          <t>-65,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-68,71%</t>
+          <t>-70,98%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-75,39; 179,54</t>
+          <t>-77,06; 151,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,5</t>
+          <t>-100,0; -34,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 76,84</t>
+          <t>-48,01; 85,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,43; 32,15</t>
+          <t>-75,45; 19,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,07; -33,25</t>
+          <t>-83,1; -34,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 61,03</t>
+          <t>-45,49; 59,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -22,07</t>
+          <t>-82,76; -17,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,87; -46,21</t>
+          <t>-84,02; -50,53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,69</t>
+          <t>-2,06; 2,73</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,39</t>
+          <t>-2,49; 2,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,53</t>
+          <t>-1,86; 2,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,01</t>
+          <t>-1,28; 5,71</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,9</t>
+          <t>-2,48; 4,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,55</t>
+          <t>-1,25; 4,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,26</t>
+          <t>-0,93; 3,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,77</t>
+          <t>-1,48; 2,83</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,79</t>
+          <t>-0,85; 2,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 255,32</t>
+          <t>-73,42; 295,44</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 282,25</t>
+          <t>-77,52; 285,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 291,74</t>
+          <t>-59,46; 279,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 296,33</t>
+          <t>-29,04; 263,24</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 233,62</t>
+          <t>-50,43; 199,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 227,72</t>
+          <t>-27,13; 211,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-36,59; 153,52</t>
+          <t>-26,42; 177,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 143,3</t>
+          <t>-40,94; 159,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 143,57</t>
+          <t>-20,16; 145,88</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>-1,92</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,99</t>
+          <t>-4,73; -1,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,8</t>
+          <t>-4,48; -0,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,08</t>
+          <t>-4,02; -0,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,39</t>
+          <t>-1,29; 3,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,85</t>
+          <t>-2,42; 1,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,8</t>
+          <t>-1,09; 2,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,63</t>
+          <t>-2,4; 0,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -0,14</t>
+          <t>-2,81; -0,02</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,32</t>
+          <t>-1,74; 1,07</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-46,36%</t>
+          <t>-46,97%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-9,82%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-26,32%</t>
+          <t>-11,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-86,58; -26,06</t>
+          <t>-87,25; -26,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-83,68; -24,0</t>
+          <t>-83,87; -20,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-72,43; -0,37</t>
+          <t>-75,43; -1,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 125,49</t>
+          <t>-27,21; 108,69</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 64,87</t>
+          <t>-50,03; 67,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 58,76</t>
+          <t>-23,63; 93,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 19,52</t>
+          <t>-49,29; 22,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -1,03</t>
+          <t>-59,66; -0,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 10,03</t>
+          <t>-35,4; 34,82</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -1,41</t>
+          <t>-4,47; -1,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,41; -2,29</t>
+          <t>-5,35; -2,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,71</t>
+          <t>-3,19; 0,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,0</t>
+          <t>-3,04; 1,91</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,65</t>
+          <t>-5,29; -0,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,93</t>
+          <t>1,29; 6,39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,12</t>
+          <t>-3,33; -0,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -1,92</t>
+          <t>-4,74; -1,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,56</t>
+          <t>-0,29; 3,01</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-53,06%</t>
+          <t>-36,62%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-84,89; -39,64</t>
+          <t>-84,26; -36,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-97,51; -59,09</t>
+          <t>-97,69; -61,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-82,25; -21,29</t>
+          <t>-62,19; 9,14</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 39,11</t>
+          <t>-39,39; 35,96</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -11,63</t>
+          <t>-65,7; -12,97</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,29; 144,22</t>
+          <t>15,79; 121,31</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-50,27; -2,68</t>
+          <t>-51,14; -1,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-75,29; -40,31</t>
+          <t>-74,66; -39,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 53,37</t>
+          <t>-4,49; 65,58</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,16</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,3</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,11</t>
+          <t>-1,59; 0,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,92</t>
+          <t>-2,31; -0,86</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,91; -0,43</t>
+          <t>-1,82; -0,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,9</t>
+          <t>-0,34; 1,9</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,3</t>
+          <t>-2,29; -0,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,2</t>
+          <t>-0,55; 1,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,64</t>
+          <t>-0,72; 0,62</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,76</t>
+          <t>-2,02; -0,84</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,17</t>
+          <t>-0,95; 0,28</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-39,75%</t>
+          <t>-35,94%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-13,43%</t>
+          <t>-7,43%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,73; -3,3</t>
+          <t>-47,8; 1,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-69,12; -35,13</t>
+          <t>-68,14; -33,94</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-57,57; -16,46</t>
+          <t>-54,17; -12,55</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 44,72</t>
+          <t>-6,1; 42,58</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-41,15; -6,34</t>
+          <t>-41,89; -6,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 26,18</t>
+          <t>-9,38; 30,58</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 17,09</t>
+          <t>-16,41; 16,59</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-47,11; -20,6</t>
+          <t>-46,62; -22,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 4,57</t>
+          <t>-21,57; 8,15</t>
         </is>
       </c>
     </row>
